--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -11814,7 +11814,7 @@
         <v>135545889</v>
       </c>
       <c r="B96" t="n">
-        <v>93409</v>
+        <v>93412</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -11814,7 +11814,7 @@
         <v>135545889</v>
       </c>
       <c r="B96" t="n">
-        <v>93412</v>
+        <v>93413</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -8042,7 +8042,7 @@
         <v>136305330</v>
       </c>
       <c r="B65" t="n">
-        <v>57927</v>
+        <v>57929</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>136305638</v>
       </c>
       <c r="B66" t="n">
-        <v>57927</v>
+        <v>57929</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>136305601</v>
       </c>
       <c r="B82" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>136305405</v>
       </c>
       <c r="B83" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>135545889</v>
       </c>
       <c r="B96" t="n">
-        <v>93413</v>
+        <v>93418</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>136472590</v>
       </c>
       <c r="B139" t="n">
-        <v>57196</v>
+        <v>57198</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>136600055</v>
       </c>
       <c r="B274" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>136600366</v>
       </c>
       <c r="B346" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -12184,7 +12184,7 @@
         <v>135545889</v>
       </c>
       <c r="B99" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -9887,7 +9887,7 @@
         <v>131444312</v>
       </c>
       <c r="B80" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>131850501</v>
       </c>
       <c r="B200" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>131850830</v>
       </c>
       <c r="B201" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>131850864</v>
       </c>
       <c r="B202" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -5764,7 +5764,7 @@
         <v>136854282</v>
       </c>
       <c r="B45" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>136983368</v>
       </c>
       <c r="B90" t="n">
-        <v>56875</v>
+        <v>56888</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>136983352</v>
       </c>
       <c r="B91" t="n">
-        <v>56889</v>
+        <v>56902</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>136840264</v>
       </c>
       <c r="B163" t="n">
-        <v>57929</v>
+        <v>57942</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>137069758</v>
       </c>
       <c r="B198" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>137069773</v>
       </c>
       <c r="B199" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>136840428</v>
       </c>
       <c r="B207" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>137069736</v>
       </c>
       <c r="B208" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>136983676</v>
       </c>
       <c r="B213" t="n">
-        <v>56887</v>
+        <v>56900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>136983620</v>
       </c>
       <c r="B214" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>137143866</v>
       </c>
       <c r="B248" t="n">
-        <v>57929</v>
+        <v>57942</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>136981483</v>
       </c>
       <c r="B275" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>136600055</v>
       </c>
       <c r="B286" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>136981301</v>
       </c>
       <c r="B339" t="n">
-        <v>57158</v>
+        <v>57171</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>136981674</v>
       </c>
       <c r="B340" t="n">
-        <v>57158</v>
+        <v>57171</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>136981311</v>
       </c>
       <c r="B341" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>136600366</v>
       </c>
       <c r="B361" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -43939,7 +43939,7 @@
         <v>136854308</v>
       </c>
       <c r="B362" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>136981526</v>
       </c>
       <c r="B363" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -44168,7 +44168,7 @@
         <v>137144000</v>
       </c>
       <c r="B364" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -44644,7 +44644,7 @@
         <v>136982249</v>
       </c>
       <c r="B368" t="n">
-        <v>56875</v>
+        <v>56888</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>136983003</v>
       </c>
       <c r="B369" t="n">
-        <v>56875</v>
+        <v>56888</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>136983176</v>
       </c>
       <c r="B370" t="n">
-        <v>56875</v>
+        <v>56888</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>136982633</v>
       </c>
       <c r="B371" t="n">
-        <v>56887</v>
+        <v>56900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>136983022</v>
       </c>
       <c r="B372" t="n">
-        <v>56887</v>
+        <v>56900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>136983158</v>
       </c>
       <c r="B373" t="n">
-        <v>56887</v>
+        <v>56900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>136983268</v>
       </c>
       <c r="B374" t="n">
-        <v>56887</v>
+        <v>56900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>136983925</v>
       </c>
       <c r="B375" t="n">
-        <v>56887</v>
+        <v>56900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>136982289</v>
       </c>
       <c r="B376" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>136983010</v>
       </c>
       <c r="B377" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>136983134</v>
       </c>
       <c r="B378" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>136983187</v>
       </c>
       <c r="B379" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>136983868</v>
       </c>
       <c r="B380" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>136983908</v>
       </c>
       <c r="B381" t="n">
-        <v>56889</v>
+        <v>56902</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ387"/>
+  <dimension ref="A1:AZ388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5764,7 +5764,7 @@
         <v>136854282</v>
       </c>
       <c r="B45" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>136983368</v>
       </c>
       <c r="B90" t="n">
-        <v>56888</v>
+        <v>56890</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>136983352</v>
       </c>
       <c r="B91" t="n">
-        <v>56902</v>
+        <v>56904</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>136840264</v>
       </c>
       <c r="B163" t="n">
-        <v>57942</v>
+        <v>57944</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>137069758</v>
       </c>
       <c r="B198" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>137069773</v>
       </c>
       <c r="B199" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>136840428</v>
       </c>
       <c r="B207" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>137069736</v>
       </c>
       <c r="B208" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>136983676</v>
       </c>
       <c r="B213" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>136983620</v>
       </c>
       <c r="B214" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>137143866</v>
       </c>
       <c r="B248" t="n">
-        <v>57942</v>
+        <v>57944</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>136981483</v>
       </c>
       <c r="B275" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>136981301</v>
       </c>
       <c r="B339" t="n">
-        <v>57171</v>
+        <v>57173</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>136981674</v>
       </c>
       <c r="B340" t="n">
-        <v>57171</v>
+        <v>57173</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>136981311</v>
       </c>
       <c r="B341" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -43939,7 +43939,7 @@
         <v>136854308</v>
       </c>
       <c r="B362" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>136981526</v>
       </c>
       <c r="B363" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -44168,7 +44168,7 @@
         <v>137144000</v>
       </c>
       <c r="B364" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -44644,7 +44644,7 @@
         <v>136982249</v>
       </c>
       <c r="B368" t="n">
-        <v>56888</v>
+        <v>56890</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>136983003</v>
       </c>
       <c r="B369" t="n">
-        <v>56888</v>
+        <v>56890</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>136983176</v>
       </c>
       <c r="B370" t="n">
-        <v>56888</v>
+        <v>56890</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>136982633</v>
       </c>
       <c r="B371" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>136983022</v>
       </c>
       <c r="B372" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>136983158</v>
       </c>
       <c r="B373" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>136983268</v>
       </c>
       <c r="B374" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>136983925</v>
       </c>
       <c r="B375" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>136982289</v>
       </c>
       <c r="B376" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>136983010</v>
       </c>
       <c r="B377" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>136983134</v>
       </c>
       <c r="B378" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>136983187</v>
       </c>
       <c r="B379" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>136983868</v>
       </c>
       <c r="B380" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -46207,10 +46207,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>136983908</v>
+        <v>137253342</v>
       </c>
       <c r="B381" t="n">
-        <v>56902</v>
+        <v>56881</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -46218,27 +46218,23 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr"/>
       <c r="I381" t="inlineStr"/>
       <c r="M381" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -46248,14 +46244,14 @@
       </c>
       <c r="P381" t="inlineStr">
         <is>
-          <t>Lövbomossen, Lövbomossen, Nrk</t>
+          <t>Boramossen, Nrk</t>
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>470803</v>
+        <v>472347</v>
       </c>
       <c r="R381" t="n">
-        <v>6542696</v>
+        <v>6541370</v>
       </c>
       <c r="S381" t="n">
         <v>20</v>
@@ -46282,22 +46278,22 @@
       </c>
       <c r="Y381" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>22:54</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>03:52</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD381" t="b">
@@ -46323,33 +46319,33 @@
       <c r="AY381" t="inlineStr"/>
       <c r="AZ381" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136983908</t>
+          <t>https://artportalen.se/Sighting/137253342</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>28786</v>
+        <v>136983908</v>
       </c>
       <c r="B382" t="n">
-        <v>58826</v>
+        <v>56904</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>208242</v>
+        <v>206002</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -46358,24 +46354,29 @@
         </is>
       </c>
       <c r="I382" t="inlineStr"/>
-      <c r="K382" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P382" t="inlineStr">
         <is>
-          <t>Ekåsa-bränningen, Nrk</t>
+          <t>Lövbomossen, Lövbomossen, Nrk</t>
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>473795</v>
+        <v>470803</v>
       </c>
       <c r="R382" t="n">
-        <v>6543467</v>
+        <v>6542696</v>
       </c>
       <c r="S382" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="T382" t="inlineStr">
         <is>
@@ -46399,17 +46400,22 @@
       </c>
       <c r="Y382" t="inlineStr">
         <is>
-          <t>1994-05-09</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>22:54</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
         <is>
-          <t>1994-05-09</t>
-        </is>
-      </c>
-      <c r="AC382" t="inlineStr">
-        <is>
-          <t>Inventerare: Ulf Tengler. Vattenbiotop: Fältdamm. Oplanerad fyndplats syns inte i kartan, Omgivning: Skog, Jordart: Sumpmark</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB382" t="inlineStr">
+        <is>
+          <t>03:52</t>
         </is>
       </c>
       <c r="AD382" t="b">
@@ -46424,31 +46430,27 @@
       <c r="AT382" t="inlineStr"/>
       <c r="AW382" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX382" t="inlineStr">
         <is>
-          <t>Via Björn Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY382" t="inlineStr">
-        <is>
-          <t>Groddjursinventering 1994 Örebro län</t>
-        </is>
-      </c>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY382" t="inlineStr"/>
       <c r="AZ382" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/28786</t>
+          <t>https://artportalen.se/Sighting/136983908</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>123816436</v>
+        <v>28786</v>
       </c>
       <c r="B383" t="n">
-        <v>58817</v>
+        <v>58826</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -46456,37 +46458,42 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P383" t="inlineStr">
         <is>
-          <t>Grönsjöbäcken Ö, Grönsjöbäcken Ö, Nrk</t>
+          <t>Ekåsa-bränningen, Nrk</t>
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>473860</v>
+        <v>473795</v>
       </c>
       <c r="R383" t="n">
-        <v>6543517</v>
+        <v>6543467</v>
       </c>
       <c r="S383" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="T383" t="inlineStr">
         <is>
@@ -46510,27 +46517,17 @@
       </c>
       <c r="Y383" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="Z383" t="inlineStr">
-        <is>
-          <t>21:02</t>
+          <t>1994-05-09</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AB383" t="inlineStr">
-        <is>
-          <t>21:02</t>
+          <t>1994-05-09</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
         <is>
-          <t>Grodor i göl bredvid Bergslagsleden</t>
+          <t>Inventerare: Ulf Tengler. Vattenbiotop: Fältdamm. Oplanerad fyndplats syns inte i kartan, Omgivning: Skog, Jordart: Sumpmark</t>
         </is>
       </c>
       <c r="AD383" t="b">
@@ -46545,27 +46542,31 @@
       <c r="AT383" t="inlineStr"/>
       <c r="AW383" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>David Tverling</t>
-        </is>
-      </c>
-      <c r="AY383" t="inlineStr"/>
+          <t>Via Björn Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY383" t="inlineStr">
+        <is>
+          <t>Groddjursinventering 1994 Örebro län</t>
+        </is>
+      </c>
       <c r="AZ383" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123816436</t>
+          <t>https://artportalen.se/Sighting/28786</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>129803076</v>
+        <v>123816436</v>
       </c>
       <c r="B384" t="n">
-        <v>106243</v>
+        <v>58817</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -46573,37 +46574,37 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>221144</v>
+        <v>208249</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I384" t="inlineStr"/>
       <c r="P384" t="inlineStr">
         <is>
-          <t>Grönsjön, Grönsjön, Nrk</t>
+          <t>Grönsjöbäcken Ö, Grönsjöbäcken Ö, Nrk</t>
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>472005</v>
+        <v>473860</v>
       </c>
       <c r="R384" t="n">
-        <v>6543107</v>
+        <v>6543517</v>
       </c>
       <c r="S384" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T384" t="inlineStr">
         <is>
@@ -46627,12 +46628,27 @@
       </c>
       <c r="Y384" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z384" t="inlineStr">
+        <is>
+          <t>21:02</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB384" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="AC384" t="inlineStr">
+        <is>
+          <t>Grodor i göl bredvid Bergslagsleden</t>
         </is>
       </c>
       <c r="AD384" t="b">
@@ -46647,27 +46663,27 @@
       <c r="AT384" t="inlineStr"/>
       <c r="AW384" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX384" t="inlineStr">
         <is>
-          <t>Anna Hammar, Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY384" t="inlineStr"/>
       <c r="AZ384" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129803076</t>
+          <t>https://artportalen.se/Sighting/123816436</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>132011491</v>
+        <v>129803076</v>
       </c>
       <c r="B385" t="n">
-        <v>98052</v>
+        <v>106243</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -46675,41 +46691,37 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>224361</v>
+        <v>221144</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I385" t="inlineStr"/>
-      <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr"/>
-      <c r="L385" t="inlineStr"/>
-      <c r="N385" t="inlineStr"/>
       <c r="P385" t="inlineStr">
         <is>
-          <t>Lövbomossen, Lövbomossen, Nrk</t>
+          <t>Grönsjön, Grönsjön, Nrk</t>
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>470849</v>
+        <v>472005</v>
       </c>
       <c r="R385" t="n">
-        <v>6542718</v>
+        <v>6543107</v>
       </c>
       <c r="S385" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T385" t="inlineStr">
         <is>
@@ -46733,27 +46745,12 @@
       </c>
       <c r="Y385" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z385" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB385" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC385" t="inlineStr">
-        <is>
-          <t>På sten</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AD385" t="b">
@@ -46762,54 +46759,57 @@
       <c r="AE385" t="b">
         <v>0</v>
       </c>
-      <c r="AF385" t="inlineStr"/>
       <c r="AG385" t="b">
         <v>0</v>
       </c>
       <c r="AT385" t="inlineStr"/>
       <c r="AW385" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX385" t="inlineStr">
         <is>
-          <t>Therese Steiner, Anna Hammar</t>
+          <t>Anna Hammar, Therese Steiner</t>
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
       <c r="AZ385" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132011491</t>
+          <t>https://artportalen.se/Sighting/129803076</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>77984560</v>
+        <v>132011491</v>
       </c>
       <c r="B386" t="n">
-        <v>102563</v>
+        <v>98052</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>265350</v>
+        <v>224361</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Vanligt jungfrulin</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Polygala vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H386" t="inlineStr"/>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
       <c r="I386" t="inlineStr"/>
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr"/>
@@ -46817,17 +46817,17 @@
       <c r="N386" t="inlineStr"/>
       <c r="P386" t="inlineStr">
         <is>
-          <t>Momossen SO om, Nrk</t>
+          <t>Lövbomossen, Lövbomossen, Nrk</t>
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>473737</v>
+        <v>470849</v>
       </c>
       <c r="R386" t="n">
-        <v>6543775</v>
+        <v>6542718</v>
       </c>
       <c r="S386" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T386" t="inlineStr">
         <is>
@@ -46851,12 +46851,27 @@
       </c>
       <c r="Y386" t="inlineStr">
         <is>
-          <t>2019-05-23</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
         <is>
-          <t>2019-05-23</t>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB386" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC386" t="inlineStr">
+        <is>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD386" t="b">
@@ -46869,70 +46884,65 @@
       <c r="AG386" t="b">
         <v>0</v>
       </c>
-      <c r="AI386" t="inlineStr">
-        <is>
-          <t>Ängsartad yta på hygge.</t>
-        </is>
-      </c>
       <c r="AT386" t="inlineStr"/>
       <c r="AW386" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX386" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Therese Steiner, Anna Hammar</t>
         </is>
       </c>
       <c r="AY386" t="inlineStr"/>
       <c r="AZ386" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77984560</t>
+          <t>https://artportalen.se/Sighting/132011491</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>228867</v>
+        <v>77984560</v>
       </c>
       <c r="B387" t="n">
-        <v>91375</v>
+        <v>102563</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>720</v>
+        <v>265350</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Vanligt jungfrulin</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
-        </is>
-      </c>
-      <c r="H387" t="inlineStr">
-        <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr"/>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr"/>
+      <c r="N387" t="inlineStr"/>
       <c r="P387" t="inlineStr">
         <is>
-          <t>Munkabäcken, Nrk</t>
+          <t>Momossen SO om, Nrk</t>
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>474688</v>
+        <v>473737</v>
       </c>
       <c r="R387" t="n">
-        <v>6543796</v>
+        <v>6543775</v>
       </c>
       <c r="S387" t="n">
         <v>10</v>
@@ -46959,17 +46969,12 @@
       </c>
       <c r="Y387" t="inlineStr">
         <is>
-          <t>2009-09-03</t>
+          <t>2019-05-23</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
         <is>
-          <t>2009-09-03</t>
-        </is>
-      </c>
-      <c r="AC387" t="inlineStr">
-        <is>
-          <t>Fyndet gjordes under en inventering av kalkbarrskogar åt Länsstyrelsen.</t>
+          <t>2019-05-23</t>
         </is>
       </c>
       <c r="AD387" t="b">
@@ -46978,31 +46983,144 @@
       <c r="AE387" t="b">
         <v>0</v>
       </c>
+      <c r="AF387" t="inlineStr"/>
       <c r="AG387" t="b">
         <v>0</v>
       </c>
       <c r="AI387" t="inlineStr">
         <is>
-          <t>Kalkbarrskog</t>
+          <t>Ängsartad yta på hygge.</t>
         </is>
       </c>
       <c r="AT387" t="inlineStr"/>
       <c r="AW387" t="inlineStr">
         <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX387" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY387" t="inlineStr"/>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77984560</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>228867</v>
+      </c>
+      <c r="B388" t="n">
+        <v>91375</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>720</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Violgubbe</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Gomphus clavatus</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr"/>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>Munkabäcken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q388" t="n">
+        <v>474688</v>
+      </c>
+      <c r="R388" t="n">
+        <v>6543796</v>
+      </c>
+      <c r="S388" t="n">
+        <v>10</v>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W388" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y388" t="inlineStr">
+        <is>
+          <t>2009-09-03</t>
+        </is>
+      </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>2009-09-03</t>
+        </is>
+      </c>
+      <c r="AC388" t="inlineStr">
+        <is>
+          <t>Fyndet gjordes under en inventering av kalkbarrskogar åt Länsstyrelsen.</t>
+        </is>
+      </c>
+      <c r="AD388" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE388" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG388" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI388" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT388" t="inlineStr"/>
+      <c r="AW388" t="inlineStr">
+        <is>
           <t>Henrik Josefsson</t>
         </is>
       </c>
-      <c r="AX387" t="inlineStr">
+      <c r="AX388" t="inlineStr">
         <is>
           <t>Tommy Pettersson</t>
         </is>
       </c>
-      <c r="AY387" t="inlineStr">
+      <c r="AY388" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
-      <c r="AZ387" t="inlineStr">
+      <c r="AZ388" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/228867</t>
         </is>
@@ -47396,6 +47514,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -5794,16 +5794,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Grönsjöbäcken, Grönsjöbäcken, Nrk</t>
@@ -9916,11 +9908,7 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -11085,11 +11073,7 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -11207,11 +11191,7 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -24144,11 +24124,7 @@
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Diamanten center, Rankemossen L, Nrk</t>
@@ -24261,11 +24237,7 @@
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Laxå, Laxå, Nrk</t>
@@ -24383,11 +24355,7 @@
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Laxå, Laxå, Nrk</t>
@@ -24505,11 +24473,7 @@
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Laxå, Laxå, Nrk</t>
@@ -25822,11 +25786,7 @@
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -25940,11 +25900,7 @@
       </c>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -41161,11 +41117,7 @@
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M339" t="inlineStr"/>
       <c r="N339" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -41283,11 +41235,7 @@
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M340" t="inlineStr"/>
       <c r="N340" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -44670,11 +44618,7 @@
         </is>
       </c>
       <c r="I368" t="inlineStr"/>
-      <c r="M368" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M368" t="inlineStr"/>
       <c r="N368" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -44792,11 +44736,7 @@
         </is>
       </c>
       <c r="I369" t="inlineStr"/>
-      <c r="M369" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M369" t="inlineStr"/>
       <c r="N369" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -44914,11 +44854,7 @@
         </is>
       </c>
       <c r="I370" t="inlineStr"/>
-      <c r="M370" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M370" t="inlineStr"/>
       <c r="N370" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -45036,11 +44972,7 @@
         </is>
       </c>
       <c r="I371" t="inlineStr"/>
-      <c r="M371" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M371" t="inlineStr"/>
       <c r="N371" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -45158,11 +45090,7 @@
         </is>
       </c>
       <c r="I372" t="inlineStr"/>
-      <c r="M372" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M372" t="inlineStr"/>
       <c r="N372" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -45280,11 +45208,7 @@
         </is>
       </c>
       <c r="I373" t="inlineStr"/>
-      <c r="M373" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M373" t="inlineStr"/>
       <c r="N373" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -45402,11 +45326,7 @@
         </is>
       </c>
       <c r="I374" t="inlineStr"/>
-      <c r="M374" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M374" t="inlineStr"/>
       <c r="N374" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -45524,11 +45444,7 @@
         </is>
       </c>
       <c r="I375" t="inlineStr"/>
-      <c r="M375" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M375" t="inlineStr"/>
       <c r="N375" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -45642,11 +45558,7 @@
       </c>
       <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr"/>
-      <c r="M376" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M376" t="inlineStr"/>
       <c r="N376" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -45760,11 +45672,7 @@
       </c>
       <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr"/>
-      <c r="M377" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M377" t="inlineStr"/>
       <c r="N377" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -45878,11 +45786,7 @@
       </c>
       <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr"/>
-      <c r="M378" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M378" t="inlineStr"/>
       <c r="N378" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -45996,11 +45900,7 @@
       </c>
       <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr"/>
-      <c r="M379" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M379" t="inlineStr"/>
       <c r="N379" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -46114,11 +46014,7 @@
       </c>
       <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr"/>
-      <c r="M380" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M380" t="inlineStr"/>
       <c r="N380" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -46232,11 +46128,7 @@
       </c>
       <c r="H381" t="inlineStr"/>
       <c r="I381" t="inlineStr"/>
-      <c r="M381" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M381" t="inlineStr"/>
       <c r="N381" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -46354,11 +46246,7 @@
         </is>
       </c>
       <c r="I382" t="inlineStr"/>
-      <c r="M382" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M382" t="inlineStr"/>
       <c r="N382" t="inlineStr">
         <is>
           <t>autobox</t>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -5764,7 +5764,7 @@
         <v>136854282</v>
       </c>
       <c r="B45" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>136983368</v>
       </c>
       <c r="B90" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>136983352</v>
       </c>
       <c r="B91" t="n">
-        <v>56914</v>
+        <v>56915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>136840264</v>
       </c>
       <c r="B163" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>137296471</v>
       </c>
       <c r="B164" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>137296480</v>
       </c>
       <c r="B165" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>137296482</v>
       </c>
       <c r="B166" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>137330719</v>
       </c>
       <c r="B176" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>137069758</v>
       </c>
       <c r="B202" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>137069773</v>
       </c>
       <c r="B203" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>137296491</v>
       </c>
       <c r="B208" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>137296485</v>
       </c>
       <c r="B210" t="n">
-        <v>58577</v>
+        <v>58579</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>136840428</v>
       </c>
       <c r="B213" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
         <v>137069736</v>
       </c>
       <c r="B214" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>137296567</v>
       </c>
       <c r="B215" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>137330751</v>
       </c>
       <c r="B216" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>137330864</v>
       </c>
       <c r="B217" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>137296599</v>
       </c>
       <c r="B218" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>136983676</v>
       </c>
       <c r="B223" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>136983620</v>
       </c>
       <c r="B224" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>137143866</v>
       </c>
       <c r="B258" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>137291629</v>
       </c>
       <c r="B259" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>137291644</v>
       </c>
       <c r="B260" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -31517,7 +31517,7 @@
         <v>137291663</v>
       </c>
       <c r="B261" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>137291969</v>
       </c>
       <c r="B263" t="n">
-        <v>57003</v>
+        <v>57004</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>137291980</v>
       </c>
       <c r="B264" t="n">
-        <v>57003</v>
+        <v>57004</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>137292016</v>
       </c>
       <c r="B265" t="n">
-        <v>57003</v>
+        <v>57004</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>136981483</v>
       </c>
       <c r="B291" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>137291905</v>
       </c>
       <c r="B292" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>137291919</v>
       </c>
       <c r="B293" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>137291926</v>
       </c>
       <c r="B294" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>137291932</v>
       </c>
       <c r="B295" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>137291733</v>
       </c>
       <c r="B297" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>137291747</v>
       </c>
       <c r="B356" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>137291759</v>
       </c>
       <c r="B357" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>137291805</v>
       </c>
       <c r="B358" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>136981301</v>
       </c>
       <c r="B363" t="n">
-        <v>57183</v>
+        <v>57184</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>136981674</v>
       </c>
       <c r="B364" t="n">
-        <v>57183</v>
+        <v>57184</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>136981311</v>
       </c>
       <c r="B365" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -46708,7 +46708,7 @@
         <v>136854308</v>
       </c>
       <c r="B386" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>136981526</v>
       </c>
       <c r="B387" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>137144000</v>
       </c>
       <c r="B388" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -47054,7 +47054,7 @@
         <v>137292037</v>
       </c>
       <c r="B389" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>137292055</v>
       </c>
       <c r="B390" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -47647,7 +47647,7 @@
         <v>136982249</v>
       </c>
       <c r="B394" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>136983003</v>
       </c>
       <c r="B395" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>136983176</v>
       </c>
       <c r="B396" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>136982633</v>
       </c>
       <c r="B397" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>136983022</v>
       </c>
       <c r="B398" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>136983158</v>
       </c>
       <c r="B399" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>136983268</v>
       </c>
       <c r="B400" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -48473,7 +48473,7 @@
         <v>136983925</v>
       </c>
       <c r="B401" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -48591,7 +48591,7 @@
         <v>136982289</v>
       </c>
       <c r="B402" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>136983010</v>
       </c>
       <c r="B403" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -48819,7 +48819,7 @@
         <v>136983134</v>
       </c>
       <c r="B404" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>136983187</v>
       </c>
       <c r="B405" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>136983868</v>
       </c>
       <c r="B406" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>137253342</v>
       </c>
       <c r="B407" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>136983908</v>
       </c>
       <c r="B408" t="n">
-        <v>56914</v>
+        <v>56915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>

--- a/artfynd/S 1909-2022 artfynd.xlsx
+++ b/artfynd/S 1909-2022 artfynd.xlsx
@@ -22009,7 +22009,7 @@
         <v>470461</v>
       </c>
       <c r="R182" t="n">
-        <v>6544251</v>
+        <v>6544252</v>
       </c>
       <c r="S182" t="n">
         <v>20</v>
